--- a/Results_experiment/exp_2/preds_1111122222333222.xlsx
+++ b/Results_experiment/exp_2/preds_1111122222333222.xlsx
@@ -660,7 +660,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D2">
-        <v>-0.1373019367456436</v>
+        <v>0.06838300824165344</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -674,7 +674,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D3">
-        <v>3.18599796295166</v>
+        <v>1.924434423446655</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -688,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>-0.139817476272583</v>
+        <v>-0.6986210346221924</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -702,7 +702,7 @@
         <v>-8.5</v>
       </c>
       <c r="D5">
-        <v>-7.746322154998779</v>
+        <v>-7.400273323059082</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -716,7 +716,7 @@
         <v>14.80000019073486</v>
       </c>
       <c r="D6">
-        <v>9.837739944458008</v>
+        <v>8.221299171447754</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -730,7 +730,7 @@
         <v>-10</v>
       </c>
       <c r="D7">
-        <v>-3.196259737014771</v>
+        <v>-4.10770845413208</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -744,7 +744,7 @@
         <v>-9.5</v>
       </c>
       <c r="D8">
-        <v>-5.067074775695801</v>
+        <v>-3.652818918228149</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -758,7 +758,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D9">
-        <v>-0.81721031665802</v>
+        <v>-2.74233078956604</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -772,7 +772,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D10">
-        <v>-3.862445592880249</v>
+        <v>-3.895481109619141</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -786,7 +786,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D11">
-        <v>5.268383979797363</v>
+        <v>7.046089649200439</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -800,7 +800,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D12">
-        <v>5.66357946395874</v>
+        <v>2.991079807281494</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -814,7 +814,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D13">
-        <v>-1.82915210723877</v>
+        <v>-1.91981840133667</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -828,7 +828,7 @@
         <v>-0.5</v>
       </c>
       <c r="D14">
-        <v>-0.1373019367456436</v>
+        <v>0.05601026117801666</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -842,7 +842,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D15">
-        <v>-0.7588194608688354</v>
+        <v>-0.7134908437728882</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -856,7 +856,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D16">
-        <v>-0.01285955309867859</v>
+        <v>1.046528100967407</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -870,7 +870,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D17">
-        <v>-4.866406917572021</v>
+        <v>-5.08434534072876</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -884,7 +884,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D18">
-        <v>4.340265274047852</v>
+        <v>4.828894138336182</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -898,7 +898,7 @@
         <v>25.79999923706055</v>
       </c>
       <c r="D19">
-        <v>11.0084114074707</v>
+        <v>9.359064102172852</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -912,7 +912,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D20">
-        <v>-2.928103446960449</v>
+        <v>-2.680505275726318</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -926,7 +926,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D21">
-        <v>-0.9813385009765625</v>
+        <v>-0.6881491541862488</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -940,7 +940,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D22">
-        <v>17.75597381591797</v>
+        <v>19.98078918457031</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -954,7 +954,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D23">
-        <v>-0.07734419405460358</v>
+        <v>0.1499339938163757</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -968,7 +968,7 @@
         <v>-13.89999961853027</v>
       </c>
       <c r="D24">
-        <v>-8.41413402557373</v>
+        <v>-8.015464782714844</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -982,7 +982,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D25">
-        <v>-0.5321532487869263</v>
+        <v>-0.6649293899536133</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -996,7 +996,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D26">
-        <v>2.979047298431396</v>
+        <v>3.220158338546753</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1010,7 +1010,7 @@
         <v>-4.5</v>
       </c>
       <c r="D27">
-        <v>-0.1340133845806122</v>
+        <v>0.02792747318744659</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1024,7 +1024,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D28">
-        <v>-0.1373019367456436</v>
+        <v>0.2197096049785614</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1038,7 +1038,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D29">
-        <v>-0.1373019367456436</v>
+        <v>0.2383565902709961</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1052,7 +1052,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D30">
-        <v>0.2037486582994461</v>
+        <v>2.591221332550049</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1066,7 +1066,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D31">
-        <v>-15.52319622039795</v>
+        <v>-18.2911205291748</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1080,7 +1080,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D32">
-        <v>-0.1373019367456436</v>
+        <v>0.2104778736829758</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1094,7 +1094,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D33">
-        <v>-3.666342735290527</v>
+        <v>-3.383548974990845</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1108,7 +1108,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D34">
-        <v>-0.1373019367456436</v>
+        <v>0.2167748361825943</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1122,7 +1122,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D35">
-        <v>5.040699481964111</v>
+        <v>6.98000955581665</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1136,7 +1136,7 @@
         <v>-7.699999809265137</v>
       </c>
       <c r="D36">
-        <v>-7.031228542327881</v>
+        <v>-6.240049362182617</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1150,7 +1150,7 @@
         <v>-21</v>
       </c>
       <c r="D37">
-        <v>-12.7297306060791</v>
+        <v>-12.52860927581787</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1164,7 +1164,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D38">
-        <v>3.5321044921875</v>
+        <v>3.800363540649414</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1178,7 +1178,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D39">
-        <v>-2.709011554718018</v>
+        <v>-3.612135887145996</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1192,7 +1192,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D40">
-        <v>2.06441330909729</v>
+        <v>2.864678382873535</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1206,7 +1206,7 @@
         <v>-15.69999980926514</v>
       </c>
       <c r="D41">
-        <v>-9.265438079833984</v>
+        <v>-8.777340888977051</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1220,7 +1220,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D42">
-        <v>1.042974352836609</v>
+        <v>3.226827383041382</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1234,7 +1234,7 @@
         <v>-9.5</v>
       </c>
       <c r="D43">
-        <v>-7.379542827606201</v>
+        <v>-7.296605110168457</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1248,7 +1248,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D44">
-        <v>4.574784278869629</v>
+        <v>5.279230117797852</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1262,7 +1262,7 @@
         <v>-15.10000038146973</v>
       </c>
       <c r="D45">
-        <v>-8.946500778198242</v>
+        <v>-9.055253028869629</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1276,7 +1276,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D46">
-        <v>6.76536226272583</v>
+        <v>5.479824542999268</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1290,7 +1290,7 @@
         <v>10.5</v>
       </c>
       <c r="D47">
-        <v>5.022880077362061</v>
+        <v>4.83534574508667</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1304,7 +1304,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D48">
-        <v>-2.233047246932983</v>
+        <v>-2.532026290893555</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1318,7 +1318,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D49">
-        <v>-1.414600491523743</v>
+        <v>-2.587718963623047</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1332,7 +1332,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D50">
-        <v>0.8752210140228271</v>
+        <v>0.2444200664758682</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1346,7 +1346,7 @@
         <v>3</v>
       </c>
       <c r="D51">
-        <v>-0.1373019367456436</v>
+        <v>0.1976833343505859</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1360,7 +1360,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D52">
-        <v>-0.1373019367456436</v>
+        <v>1.028971672058105</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1374,7 +1374,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D53">
-        <v>12.33669853210449</v>
+        <v>16.38283157348633</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1388,7 +1388,7 @@
         <v>-28.20000076293945</v>
       </c>
       <c r="D54">
-        <v>-17.30195426940918</v>
+        <v>-19.14916610717773</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1402,7 +1402,7 @@
         <v>-15.19999980926514</v>
       </c>
       <c r="D55">
-        <v>-7.045022010803223</v>
+        <v>-6.901899814605713</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1416,7 +1416,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D56">
-        <v>-3.200523853302002</v>
+        <v>-3.306858539581299</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1430,7 +1430,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D57">
-        <v>1.700632333755493</v>
+        <v>3.448931217193604</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1444,7 +1444,7 @@
         <v>-8.5</v>
       </c>
       <c r="D58">
-        <v>-9.114969253540039</v>
+        <v>-7.84438943862915</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1458,7 +1458,7 @@
         <v>-11.89999961853027</v>
       </c>
       <c r="D59">
-        <v>-8.634514808654785</v>
+        <v>-8.835643768310547</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1472,7 +1472,7 @@
         <v>-7.5</v>
       </c>
       <c r="D60">
-        <v>-1.16701328754425</v>
+        <v>-2.084491014480591</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1486,7 +1486,7 @@
         <v>-12.60000038146973</v>
       </c>
       <c r="D61">
-        <v>-4.712987899780273</v>
+        <v>-4.861675262451172</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1500,7 +1500,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D62">
-        <v>4.814486980438232</v>
+        <v>3.493040084838867</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1514,7 +1514,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D63">
-        <v>2.075510501861572</v>
+        <v>1.913191795349121</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1528,7 +1528,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D64">
-        <v>-0.1373019367456436</v>
+        <v>0.1367477178573608</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1542,7 +1542,7 @@
         <v>-26.70000076293945</v>
       </c>
       <c r="D65">
-        <v>-15.5704517364502</v>
+        <v>-17.64394569396973</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1556,7 +1556,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D66">
-        <v>-0.14382004737854</v>
+        <v>0.1423040330410004</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1570,7 +1570,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="D67">
-        <v>13.29707527160645</v>
+        <v>12.44524669647217</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1584,7 +1584,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D68">
-        <v>4.013991355895996</v>
+        <v>3.840423583984375</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1598,7 +1598,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D69">
-        <v>-0.3166043758392334</v>
+        <v>0.2023657858371735</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1612,7 +1612,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D70">
-        <v>4.143040180206299</v>
+        <v>3.841209411621094</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1626,7 +1626,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D71">
-        <v>3.165600538253784</v>
+        <v>3.578425407409668</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1640,7 +1640,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D72">
-        <v>-0.2872940003871918</v>
+        <v>-0.5415059924125671</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1654,7 +1654,7 @@
         <v>3.5</v>
       </c>
       <c r="D73">
-        <v>2.6438889503479</v>
+        <v>3.504463911056519</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1668,7 +1668,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D74">
-        <v>0.6320907473564148</v>
+        <v>4.04097843170166</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1682,7 +1682,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D75">
-        <v>7.374963760375977</v>
+        <v>4.355648994445801</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1696,7 +1696,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D76">
-        <v>-0.1373019367456436</v>
+        <v>0.1683191955089569</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1710,7 +1710,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D77">
-        <v>0.1270908564329147</v>
+        <v>0.3215921521186829</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1724,7 +1724,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D78">
-        <v>-1.074231266975403</v>
+        <v>-0.6684271693229675</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1738,7 +1738,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D79">
-        <v>-1.326318740844727</v>
+        <v>7.444761276245117</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1752,7 +1752,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D80">
-        <v>-1.594612598419189</v>
+        <v>-2.765990257263184</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1766,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="D81">
-        <v>2.336863994598389</v>
+        <v>2.060257196426392</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1780,7 +1780,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D82">
-        <v>1.540696144104004</v>
+        <v>0.9249439835548401</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1794,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>-1.149031400680542</v>
+        <v>-0.3668296933174133</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1808,7 +1808,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D84">
-        <v>-5.012423038482666</v>
+        <v>-5.093098640441895</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1822,7 +1822,7 @@
         <v>-12.89999961853027</v>
       </c>
       <c r="D85">
-        <v>-11.55624675750732</v>
+        <v>-10.86086082458496</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1836,7 +1836,7 @@
         <v>-2.5</v>
       </c>
       <c r="D86">
-        <v>-2.225131034851074</v>
+        <v>-2.022359371185303</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1850,7 +1850,7 @@
         <v>-0.5</v>
       </c>
       <c r="D87">
-        <v>-0.5460547804832458</v>
+        <v>-0.616880476474762</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1864,7 +1864,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D88">
-        <v>3.001904010772705</v>
+        <v>4.187750816345215</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1878,7 +1878,7 @@
         <v>-1</v>
       </c>
       <c r="D89">
-        <v>-1.302093029022217</v>
+        <v>-0.4278783202171326</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1892,7 +1892,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D90">
-        <v>-6.637222766876221</v>
+        <v>-6.777197360992432</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1906,7 +1906,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D91">
-        <v>0.3444076180458069</v>
+        <v>2.603191137313843</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1920,7 +1920,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D92">
-        <v>-2.307514429092407</v>
+        <v>-2.228818893432617</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1934,7 +1934,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D93">
-        <v>-0.1373019367456436</v>
+        <v>0.2212205529212952</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1948,7 +1948,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D94">
-        <v>-0.858730673789978</v>
+        <v>-0.7140052318572998</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1962,7 +1962,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D95">
-        <v>-0.05280753970146179</v>
+        <v>0.3722168803215027</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1976,7 +1976,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D96">
-        <v>-0.1373019367456436</v>
+        <v>0.160205751657486</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1990,7 +1990,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D97">
-        <v>5.571463584899902</v>
+        <v>5.943143367767334</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2004,7 +2004,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D98">
-        <v>-9.203823089599609</v>
+        <v>-7.827476024627686</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2018,7 +2018,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D99">
-        <v>6.119500637054443</v>
+        <v>4.651278495788574</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2032,7 +2032,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D100">
-        <v>-0.8903274536132812</v>
+        <v>-1.509874582290649</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2046,7 +2046,7 @@
         <v>-15.60000038146973</v>
       </c>
       <c r="D101">
-        <v>-15.345871925354</v>
+        <v>-16.76633644104004</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2060,7 +2060,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D102">
-        <v>-0.1230413764715195</v>
+        <v>0.9773684144020081</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2074,7 +2074,7 @@
         <v>-12.5</v>
       </c>
       <c r="D103">
-        <v>-7.575263977050781</v>
+        <v>-8.507035255432129</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2088,7 +2088,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D104">
-        <v>4.697958469390869</v>
+        <v>5.443572521209717</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2102,7 +2102,7 @@
         <v>17.60000038146973</v>
       </c>
       <c r="D105">
-        <v>11.69779300689697</v>
+        <v>8.113201141357422</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2116,7 +2116,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D106">
-        <v>8.984221458435059</v>
+        <v>6.250863552093506</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2130,7 +2130,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D107">
-        <v>-0.1373019367456436</v>
+        <v>0.2212205529212952</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2144,7 +2144,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D108">
-        <v>2.14423394203186</v>
+        <v>0.8305045962333679</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2158,7 +2158,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D109">
-        <v>1.092433452606201</v>
+        <v>2.651821136474609</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2172,7 +2172,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D110">
-        <v>-1.003388047218323</v>
+        <v>-1.639503002166748</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2186,7 +2186,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D111">
-        <v>6.718517780303955</v>
+        <v>7.026797294616699</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2200,7 +2200,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D112">
-        <v>-0.08686448633670807</v>
+        <v>0.5517173409461975</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2214,7 +2214,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D113">
-        <v>-1.637295007705688</v>
+        <v>-1.795182228088379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2228,7 +2228,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D114">
-        <v>-7.250616550445557</v>
+        <v>-6.044716835021973</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2242,7 +2242,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D115">
-        <v>8.760370254516602</v>
+        <v>8.699795722961426</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2256,7 +2256,7 @@
         <v>39.70000076293945</v>
       </c>
       <c r="D116">
-        <v>0.9521415233612061</v>
+        <v>0.4726100265979767</v>
       </c>
     </row>
   </sheetData>
